--- a/renads-api/TramaCargaEstudiante.xlsx
+++ b/renads-api/TramaCargaEstudiante.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\renads\renads-api\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E0C6CA6-70AD-465D-AB30-89AB6CCA3174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF7D555-0E86-4608-AE6C-C4BAF7DC1BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="carga" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>numero_documento</t>
   </si>
@@ -82,25 +82,28 @@
     <t>2025-01</t>
   </si>
   <si>
-    <t>ESTERFILIA ISABEL</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>PULACHE</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>ISABEL@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>JESUS MARIA</t>
-  </si>
-  <si>
-    <t>U323232</t>
+    <t>PEDRO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>PLOPEZ@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>AV. AREQUIPA 810</t>
+  </si>
+  <si>
+    <t>34533445</t>
+  </si>
+  <si>
+    <t>U32544</t>
   </si>
 </sst>
 </file>
@@ -462,13 +465,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="52.8">
+    <row r="1" spans="1:20" ht="51">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -528,8 +531,8 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2">
-        <v>40920946</v>
+      <c r="B2" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -550,7 +553,7 @@
         <v>24</v>
       </c>
       <c r="I2">
-        <v>948575784</v>
+        <v>932445784</v>
       </c>
       <c r="J2" t="s">
         <v>25</v>
@@ -568,10 +571,10 @@
         <v>19</v>
       </c>
       <c r="P2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Q2">
-        <v>17.600000000000001</v>
+        <v>14.6</v>
       </c>
     </row>
   </sheetData>
